--- a/Result/profitability/3541.xlsx
+++ b/Result/profitability/3541.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01125</v>
+        <v>0.045</v>
       </c>
       <c r="N2" t="n">
-        <v>35.1425</v>
+        <v>35.2475</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.15125</v>
+        <v>0.09749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>34.51125</v>
+        <v>34.33625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18125</v>
+        <v>0.185</v>
       </c>
       <c r="N4" t="n">
-        <v>33.85625</v>
+        <v>33.87625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.325</v>
+        <v>0.4725</v>
       </c>
       <c r="N5" t="n">
-        <v>33.72875</v>
+        <v>33.74125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4974999999999999</v>
+        <v>0.47125</v>
       </c>
       <c r="N6" t="n">
-        <v>33.055</v>
+        <v>33.64875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.485</v>
+        <v>0.51</v>
       </c>
       <c r="N7" t="n">
-        <v>32.51125</v>
+        <v>32.46375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5725</v>
+        <v>0.58</v>
       </c>
       <c r="N8" t="n">
-        <v>31.55625</v>
+        <v>31.6275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3541</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>260</v>
+      </c>
+      <c r="D75" t="n">
+        <v>166</v>
+      </c>
+      <c r="E75" t="n">
+        <v>94</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.04750000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5700000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0160744500846024</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.082568807339449</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.002783189535207287</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
